--- a/tarea1-gestor-contrasenas/docs/mcu5/excel/01-controles-mcu5-perfil-avanzado.xlsx
+++ b/tarea1-gestor-contrasenas/docs/mcu5/excel/01-controles-mcu5-perfil-avanzado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Controles MCU5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles MCU5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -994,12 +994,12 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>docs/09-Gestion-Accesos.md, tabla 'Evidencia pendiente'</t>
+          <t>docs/09-Gestion-Accesos.md (TOTP de la bóveda y del panel; capturas de enroll pendientes)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: TOTP/WebAuthn/Windows Hello no implementados aun (meta H3, 02/10); no se puede demostrar en vivo hoy.</t>
+          <t>TOTP implementado en la bóveda y en el panel (enroll y login con código). Limitación documentada: WebAuthn y Windows Hello fuera de la entrega, ver docs/09-Gestion-Accesos.md, sección 'Limitación de alcance: Windows Hello y WebAuthn'.</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>cliente-gestor/src-tauri/src/crypto/ (Argon2id + XChaCha20-Poly1305, hoy son stubs con TODO)</t>
+          <t>cliente-gestor/src-tauri/src/crypto/ (cifrado en reposo) y docs/00-arquitectura-c4.md (flujos de tránsito)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de implementacion real; hoy kdf.rs y cipher.rs no tienen logica. TLS 1.2+ en transito tambien pendiente de desplegar.</t>
+          <t>Cifrado de la bóveda en reposo (Argon2id + XChaCha20-Poly1305), con test de que el secreto no queda en texto plano. Limitación documentada: TLS en tránsito fuera de la entrega, ver docs/00-arquitectura-c4.md, sección 'Limitación de alcance: TLS en el laboratorio'.</t>
         </is>
       </c>
     </row>

--- a/tarea1-gestor-contrasenas/docs/mcu5/excel/01-controles-mcu5-perfil-avanzado.xlsx
+++ b/tarea1-gestor-contrasenas/docs/mcu5/excel/01-controles-mcu5-perfil-avanzado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles MCU5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Controles MCU5" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Mostrar el documento y su historial de versiones; aprobacion formal del RSI pendiente antes del 14/10.</t>
+          <t>Mostrar el documento. La aprobación formal del RSI sigue pendiente (Andrés).</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Encabezados de mapeo normativo de cada doc en docs/ + docs/11-SoA-Plan-Tratamiento.md (pendiente)</t>
+          <t>docs/11-SoA-Plan-Tratamiento.md (93 controles, 07/10). Falta firma del RSI.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Mostrar la seccion 6 con fechas objetivo cargadas; la aceptacion formal (firma del RSI) es un pendiente explicito antes del 07/10.</t>
+          <t>Mostrar el documento. La aprobación formal del RSI sigue pendiente (Andrés).</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>docs/10-Gestion-Vulnerabilidades.md (pendiente de escribir, meta 01-05/10)</t>
+          <t>docs/10-Gestion-Vulnerabilidades.md; evidencias 10-pip-audit*.txt, 10-bandit.txt, 10-npm-audit.txt. V03 remediada. Red/Trivy/cargo audit pendientes.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: requiere correr escaneos SAST/DAST/OpenVAS antes de poder demostrarlo.</t>
+          <t>Mostrar el registro V01-V04 y los txt de evidencias. Declarar que nmap/Trivy no se corrieron.</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de implementacion: RBAC de control-central/app/api/users.py sigue siendo un TODO. Hoy se demuestra el diseno, no el alta/baja real.</t>
+          <t>POST /api/users/ y login con TOTP (B-14). Ya no es un TODO.</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>docs/09-Gestion-Accesos.md (TOTP de la bóveda y del panel; capturas de enroll pendientes)</t>
+          <t>docs/09-Gestion-Accesos.md; guia C-09 (bóveda) y B-14 (panel). Hello/WebAuthn fuera de alcance.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Diseno de clave JWS unica por agente (cliente-gestor/src-tauri/src/events/signer.rs) + RBAC de control-central (pendiente)</t>
+          <t>control-central/app/api/users.py; guia-de-pruebas.md B-14; usuario rsi@correo.local. Roles admin/auditor/rsi.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de despliegue: mostrar que un agente comprometido no puede firmar eventos de otro (R02 en 03-Analisis-Riesgos.md).</t>
+          <t>POST /api/users/ y login con TOTP (B-14). Ya no es un TODO.</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>docs/06-Plan-Continuidad.md (pendiente, meta 28/09-01/10)</t>
+          <t>docs/09-Gestion-Accesos.md; cliente-gestor (Argon2id, XChaCha20, TOTP); docs/evidencias/05-03-app-alta.png; guia-de-pruebas.md C-09. Hello/WebAuthn y TLS: limitación documentada.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: falta escribir el plan y ejecutar una prueba de restauracion real.</t>
+          <t>Abrir la app, TOTP, alta firmada (C-04). Declarar Hello/TLS como limitación.</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de hardening real: hoy es un Dockerfile basico (python:3.12-slim) sin checklist de endurecimiento aplicado.</t>
+          <t>Abrir la app, TOTP, alta firmada (C-04). Declarar Hello/TLS como limitación.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: Wazuh todavia no esta desplegado (meta H2, 29/09).</t>
+          <t>Abrir la app, TOTP, alta firmada (C-04). Declarar Hello/TLS como limitación.</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>docs/10-Gestion-Vulnerabilidades.md (pendiente)</t>
+          <t>docs/10-Gestion-Vulnerabilidades.md; evidencias 10-pip-audit*.txt, 10-bandit.txt, 10-npm-audit.txt. V03 remediada. Red/Trivy/cargo audit pendientes.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: requiere escaneos y su cierre con plazos, aun no realizados.</t>
+          <t>Mostrar el registro V01-V04 y los txt de evidencias. Declarar que nmap/Trivy no se corrieron.</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: ningun SAST (semgrep/bandit) corrido aun sobre control-central</t>
+          <t>docs/10-Gestion-Vulnerabilidades.md; evidencias 10-pip-audit*.txt, 10-bandit.txt, 10-npm-audit.txt. V03 remediada. Red/Trivy/cargo audit pendientes.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de despliegue (meta H2, 29/09).</t>
+          <t>Mostrar /api/alerts/, Grafana y docker exec ... tail alerts.json (regla 100120).</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: el forwarder es hoy un stub sin logica de reenvio real.</t>
+          <t>Mostrar /api/alerts/, Grafana y docker exec ... tail alerts.json (regla 100120).</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de creacion real (meta 28/09-01/10, ver docs/07-Monitoreo-Logs-SIEM.md, aun sin escribir).</t>
+          <t>Mostrar /api/alerts/, Grafana y docker exec ... tail alerts.json (regla 100120).</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de implementacion.</t>
+          <t>Mostrar /api/alerts/, Grafana y docker exec ... tail alerts.json (regla 100120).</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de despliegue de Mailu (meta 29/09) y de disparar un correo real de prueba ante un evento de alta/cambio de maestra.</t>
+          <t>Mostrar /api/alerts/, Grafana y docker exec ... tail alerts.json (regla 100120).</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: infra/grafana/provisioning/ todavia no tiene datasources ni dashboards cargados.</t>
+          <t>Mostrar /api/alerts/, Grafana y docker exec ... tail alerts.json (regla 100120).</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>docs/04-Gestion-Incidentes.md (pendiente, meta 02-05/10)</t>
+          <t>docs/04-gestion-incidentes.md; docs/12-Notificacion-Incidentes.md; POST/PATCH /api/incidents/; incidente 1 en docs/evidencias/06-restauracion-bd-con-datos.txt. Falta firma RSI y contactos oficiales.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de escribir.</t>
+          <t>GET /api/incidents/ y el incidente 1 en 12 y en la restauración.</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>docs/04-Gestion-Incidentes.md + registro de incidente simulado (entregable de la seccion 6.2 de LETRA.md, pendiente)</t>
+          <t>docs/04-gestion-incidentes.md; docs/12-Notificacion-Incidentes.md; POST/PATCH /api/incidents/; incidente 1 en docs/evidencias/06-restauracion-bd-con-datos.txt. Falta firma RSI y contactos oficiales.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: falta simular al menos un incidente completo (deteccion a cierre) antes del 07/10.</t>
+          <t>GET /api/incidents/ y el incidente 1 en 12 y en la restauración.</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>docs/04-Gestion-Incidentes.md (pendiente)</t>
+          <t>docs/04-gestion-incidentes.md; docs/12-Notificacion-Incidentes.md; POST/PATCH /api/incidents/; incidente 1 en docs/evidencias/06-restauracion-bd-con-datos.txt. Falta firma RSI y contactos oficiales.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Pendiente, depende del incidente simulado.</t>
+          <t>GET /api/incidents/ y el incidente 1 en 12 y en la restauración.</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>docs/12-Notificacion-Incidentes.md (pendiente, meta 05-07/10)</t>
+          <t>docs/04-gestion-incidentes.md; docs/12-Notificacion-Incidentes.md; POST/PATCH /api/incidents/; incidente 1 en docs/evidencias/06-restauracion-bd-con-datos.txt. Falta firma RSI y contactos oficiales.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de escribir; se basa en un borrador de notificacion simulada BCU/URCDP.</t>
+          <t>GET /api/incidents/ y el incidente 1 en 12 y en la restauración.</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>docs/06-Plan-Continuidad.md (pendiente, meta 28/09-01/10)</t>
+          <t>docs/06-Plan-Continuidad.md; scripts/backup_bd.sh; docs/evidencias/06-restauracion-bd.txt y 06-restauracion-bd-con-datos.txt. Backup diario y copia fuera del equipo pendientes.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de escribir y de ejecutar una prueba de restauracion.</t>
+          <t>Repetir scripts/restaurar_bd_prueba.sh y mostrar el SHA-256 del dump.</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>docs/06-Plan-Continuidad.md (pendiente)</t>
+          <t>docs/06-Plan-Continuidad.md; scripts/backup_bd.sh; docs/evidencias/06-restauracion-bd.txt y 06-restauracion-bd-con-datos.txt. Backup diario y copia fuera del equipo pendientes.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Pendiente: requiere ejecutar una restauracion real de un backup de PostgreSQL o de una boveda exportada.</t>
+          <t>Repetir scripts/restaurar_bd_prueba.sh y mostrar el SHA-256 del dump.</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>docs/06-Plan-Continuidad.md (pendiente)</t>
+          <t>docs/06-Plan-Continuidad.md; scripts/backup_bd.sh; docs/evidencias/06-restauracion-bd.txt y 06-restauracion-bd-con-datos.txt. Backup diario y copia fuera del equipo pendientes.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Pendiente de escribir la secuencia de reanudacion de servicios.</t>
+          <t>Repetir scripts/restaurar_bd_prueba.sh y mostrar el SHA-256 del dump.</t>
         </is>
       </c>
     </row>
